--- a/DataAnalysis/TryingToPackStuffBetter/PreprocessingRTandDIM/LC/0.05/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/PreprocessingRTandDIM/LC/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\PreprocessingRTandDIM\LC\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863399D3-A2C8-4DB8-8E0E-2A5711CCA923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A08F79D-9E1D-49C4-98D7-142180E43487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,8 +165,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -492,34 +493,34 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>14.416666666666666</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>2.5922378304655913</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>18.916666666666668</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>2.9835407071992797</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>31.708333333333332</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>2.8955948779084579</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>21.680555555555554</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>1.3492578082029512</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>7.5972222222222223</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>2.3218965747215541</v>
       </c>
     </row>
@@ -527,34 +528,34 @@
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>12.625</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>1.7060815589280267</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>16.5625</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>3.2120031577995509</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>31.6875</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>5.951815449327805</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>20.291666666666668</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>2.4636242498490732</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>7.9791666666666661</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>1.3405681690511067</v>
       </c>
     </row>
@@ -562,36 +563,46 @@
       <c r="B5" t="s">
         <v>28</v>
       </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D6">
+      <c r="D6" s="1">
         <v>13.1875</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>2.4044230077089179</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>18</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>2.8908723349782948</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>34.9375</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>3.3640696017939771</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>22.041666666666664</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>1.6565167125772136</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>8.9791666666666679</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>2.0863074009906968</v>
       </c>
     </row>
@@ -599,34 +610,34 @@
       <c r="C7" t="s">
         <v>29</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>13.416666666666666</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>1.715128760958387</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>18.833333333333332</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>3.0930028559098837</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>30.416666666666668</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>4.4318919962772787</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>20.888888888888889</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>1.5551586795303298</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>7.4722222222222214</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>2.9465925078652164</v>
       </c>
     </row>
